--- a/docs/utm-ssylki.xlsx
+++ b/docs/utm-ssylki.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="114">
   <si>
     <t>Справочник значений</t>
   </si>
@@ -78,6 +78,12 @@
     <t>https://legalcareerist.ru/kadry/vacancies</t>
   </si>
   <si>
+    <t>Вакансия «Младший юрист», КГ «ТИМ»</t>
+  </si>
+  <si>
+    <t>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim</t>
+  </si>
+  <si>
     <t>Сообщество (подписка)</t>
   </si>
   <si>
@@ -277,6 +283,15 @@
   </si>
   <si>
     <t>Пример кампании: вакансии месяца</t>
+  </si>
+  <si>
+    <t>vacancy_tim_junior</t>
+  </si>
+  <si>
+    <t>Вакансия №47, пост в Telegram-канале</t>
+  </si>
+  <si>
+    <t>Вакансия №47, пост в ВКонтакте</t>
   </si>
   <si>
     <t>materials_oktober</t>
@@ -783,12 +798,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="66" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -800,10 +815,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="44" customHeight="1">
@@ -811,7 +826,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -820,16 +835,16 @@
         <v>6</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -838,13 +853,13 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7" t="str">
@@ -852,7 +867,7 @@
         <v>https://legalcareerist.ru/?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -861,13 +876,13 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7" t="str">
@@ -875,7 +890,7 @@
         <v>https://legalcareerist.ru/?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -884,13 +899,13 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="str">
@@ -898,7 +913,7 @@
         <v>https://legalcareerist.ru/kadry/employers?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -907,13 +922,13 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="7" t="str">
@@ -921,7 +936,7 @@
         <v>https://legalcareerist.ru/kadry/employers?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -930,13 +945,13 @@
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="7" t="str">
@@ -944,7 +959,7 @@
         <v>https://legalcareerist.ru/kadry/candidates?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -953,13 +968,13 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7" t="str">
@@ -967,22 +982,22 @@
         <v>https://legalcareerist.ru/kadry/candidates?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7" t="str">
@@ -990,22 +1005,22 @@
         <v>https://legalcareerist.ru/community?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7" t="str">
@@ -1013,22 +1028,22 @@
         <v>https://legalcareerist.ru/community?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7" t="str">
@@ -1036,22 +1051,22 @@
         <v>https://legalcareerist.ru/events?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7" t="str">
@@ -1059,22 +1074,22 @@
         <v>https://legalcareerist.ru/events?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7" t="str">
@@ -1082,22 +1097,22 @@
         <v>https://legalcareerist.ru/marketplace?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7" t="str">
@@ -1105,22 +1120,22 @@
         <v>https://legalcareerist.ru/marketplace?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7" t="str">
@@ -1128,22 +1143,22 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7" t="str">
@@ -1151,22 +1166,22 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=telegram&amp;utm_medium=story&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7" t="str">
@@ -1174,22 +1189,22 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=telegram&amp;utm_medium=ads&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7" t="str">
@@ -1197,22 +1212,22 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=vk&amp;utm_medium=post&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7" t="str">
@@ -1220,22 +1235,22 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=vk&amp;utm_medium=story&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7" t="str">
@@ -1243,7 +1258,7 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=vk&amp;utm_medium=ads&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1252,13 +1267,13 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7" t="str">
@@ -1266,7 +1281,7 @@
         <v>https://legalcareerist.ru/kadry/vacancies?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=oktober_vacancies</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1275,13 +1290,13 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7" t="str">
@@ -1289,103 +1304,123 @@
         <v>https://legalcareerist.ru/kadry/vacancies?utm_source=vk&amp;utm_medium=post&amp;utm_campaign=oktober_vacancies</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7" t="str">
         <f>IF(OR(IF(B25&lt;&gt;"",B25,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A25,'Справочник'!$A$5:$A$30,0)),""))="",C25="",D25="",E25=""),"",IF(B25&lt;&gt;"",B25,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A25,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B25&lt;&gt;"",B25,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A25,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C25&amp;"&amp;utm_medium="&amp;D25&amp;"&amp;utm_campaign="&amp;E25&amp;IF(F25&lt;&gt;"","&amp;utm_content="&amp;F25,""))</f>
-        <v>https://legalcareerist.ru/materials/longlist-studencheskie-yuridicheskie-meropriyatiya?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+        <v>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=vacancy_tim_junior</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7" t="str">
         <f>IF(OR(IF(B26&lt;&gt;"",B26,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A26,'Справочник'!$A$5:$A$30,0)),""))="",C26="",D26="",E26=""),"",IF(B26&lt;&gt;"",B26,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A26,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B26&lt;&gt;"",B26,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A26,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C26&amp;"&amp;utm_medium="&amp;D26&amp;"&amp;utm_campaign="&amp;E26&amp;IF(F26&lt;&gt;"","&amp;utm_content="&amp;F26,""))</f>
-        <v>https://legalcareerist.ru/materials/gaid-kariera-yurista-v-notariate?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+        <v>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim?utm_source=vk&amp;utm_medium=post&amp;utm_campaign=vacancy_tim_junior</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7" t="str">
         <f>IF(OR(IF(B27&lt;&gt;"",B27,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A27,'Справочник'!$A$5:$A$30,0)),""))="",C27="",D27="",E27=""),"",IF(B27&lt;&gt;"",B27,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A27,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B27&lt;&gt;"",B27,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A27,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C27&amp;"&amp;utm_medium="&amp;D27&amp;"&amp;utm_campaign="&amp;E27&amp;IF(F27&lt;&gt;"","&amp;utm_content="&amp;F27,""))</f>
+        <v>https://legalcareerist.ru/materials/longlist-studencheskie-yuridicheskie-meropriyatiya?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="7" t="str">
+        <f>IF(OR(IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),""))="",C28="",D28="",E28=""),"",IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C28&amp;"&amp;utm_medium="&amp;D28&amp;"&amp;utm_campaign="&amp;E28&amp;IF(F28&lt;&gt;"","&amp;utm_content="&amp;F28,""))</f>
+        <v>https://legalcareerist.ru/materials/gaid-kariera-yurista-v-notariate?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="7" t="str">
+        <f>IF(OR(IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),""))="",C29="",D29="",E29=""),"",IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C29&amp;"&amp;utm_medium="&amp;D29&amp;"&amp;utm_campaign="&amp;E29&amp;IF(F29&lt;&gt;"","&amp;utm_content="&amp;F29,""))</f>
         <v>https://legalcareerist.ru/materials/gaid-stipendii-i-granty?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7">
-        <f>IF(OR(IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),""))="",C28="",D28="",E28=""),"",IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C28&amp;"&amp;utm_medium="&amp;D28&amp;"&amp;utm_campaign="&amp;E28&amp;IF(F28&lt;&gt;"","&amp;utm_content="&amp;F28,""))</f>
-        <v/>
-      </c>
-      <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7">
-        <f>IF(OR(IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),""))="",C29="",D29="",E29=""),"",IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C29&amp;"&amp;utm_medium="&amp;D29&amp;"&amp;utm_campaign="&amp;E29&amp;IF(F29&lt;&gt;"","&amp;utm_content="&amp;F29,""))</f>
-        <v/>
-      </c>
-      <c r="H29" s="8"/>
+      <c r="H29" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="6"/>
@@ -3748,16 +3783,16 @@
         <v>8</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3768,16 +3803,16 @@
         <v>10</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3788,16 +3823,16 @@
         <v>12</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3808,16 +3843,16 @@
         <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3828,16 +3863,16 @@
         <v>16</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3848,16 +3883,16 @@
         <v>18</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3868,16 +3903,16 @@
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3888,16 +3923,16 @@
         <v>22</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3908,16 +3943,16 @@
         <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3928,10 +3963,10 @@
         <v>26</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="8"/>
@@ -3985,8 +4020,12 @@
       <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="D19" s="6"/>
       <c r="E19" s="8"/>
       <c r="G19" s="6"/>
@@ -4099,6 +4138,7 @@
     <hyperlink ref="B16" r:id="rId12"/>
     <hyperlink ref="B17" r:id="rId13"/>
     <hyperlink ref="B18" r:id="rId14"/>
+    <hyperlink ref="B19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4115,87 +4155,87 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="42" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="42" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="42" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="42" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/docs/utm-ssylki.xlsx
+++ b/docs/utm-ssylki.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="118">
   <si>
     <t>Справочник значений</t>
   </si>
@@ -144,6 +144,12 @@
     <t>ВКонтакте</t>
   </si>
   <si>
+    <t>instagram</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
     <t>youtube</t>
   </si>
   <si>
@@ -294,6 +300,15 @@
     <t>Вакансия №47, пост в ВКонтакте</t>
   </si>
   <si>
+    <t>Вакансия №47, сторис в Telegram</t>
+  </si>
+  <si>
+    <t>Вакансия №47, сторис в Instagram</t>
+  </si>
+  <si>
+    <t>Вакансия №47, сторис ВКонтакте</t>
+  </si>
+  <si>
     <t>materials_oktober</t>
   </si>
   <si>
@@ -357,10 +372,7 @@
     <t>Счётчик Метрики включается после «Принять» в окне про cookie, поэтому в Метрике будут посетители, согласившиеся на cookie. Источник в уведомлении о заявке от этого не зависит.</t>
   </si>
   <si>
-    <t>Instagram</t>
-  </si>
-  <si>
-    <t>В списке источников Instagram нет сознательно: в России он заблокирован, а компания Meta признана экстремистской организацией, публиковать ссылки там не стоит. Остальные площадки добавляйте на листе «Справочник».</t>
+    <t>Добавлен в список источников по запросу. В России он заблокирован, а компания Meta признана экстремистской организацией.</t>
   </si>
 </sst>
 </file>
@@ -798,12 +810,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="66" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -815,10 +827,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="44" customHeight="1">
@@ -826,7 +838,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -835,16 +847,16 @@
         <v>6</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,10 +868,10 @@
         <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7" t="str">
@@ -867,7 +879,7 @@
         <v>https://legalcareerist.ru/?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -879,10 +891,10 @@
         <v>39</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7" t="str">
@@ -890,7 +902,7 @@
         <v>https://legalcareerist.ru/?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -902,10 +914,10 @@
         <v>37</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="str">
@@ -913,7 +925,7 @@
         <v>https://legalcareerist.ru/kadry/employers?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -925,10 +937,10 @@
         <v>39</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="7" t="str">
@@ -936,7 +948,7 @@
         <v>https://legalcareerist.ru/kadry/employers?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -948,10 +960,10 @@
         <v>37</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="7" t="str">
@@ -959,7 +971,7 @@
         <v>https://legalcareerist.ru/kadry/candidates?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -971,10 +983,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7" t="str">
@@ -982,7 +994,7 @@
         <v>https://legalcareerist.ru/kadry/candidates?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -994,10 +1006,10 @@
         <v>37</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7" t="str">
@@ -1005,7 +1017,7 @@
         <v>https://legalcareerist.ru/community?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1017,10 +1029,10 @@
         <v>39</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7" t="str">
@@ -1028,7 +1040,7 @@
         <v>https://legalcareerist.ru/community?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1040,10 +1052,10 @@
         <v>37</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7" t="str">
@@ -1051,7 +1063,7 @@
         <v>https://legalcareerist.ru/events?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1063,10 +1075,10 @@
         <v>39</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7" t="str">
@@ -1074,7 +1086,7 @@
         <v>https://legalcareerist.ru/events?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1086,10 +1098,10 @@
         <v>37</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7" t="str">
@@ -1097,7 +1109,7 @@
         <v>https://legalcareerist.ru/marketplace?utm_source=telegram&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1109,10 +1121,10 @@
         <v>39</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7" t="str">
@@ -1120,7 +1132,7 @@
         <v>https://legalcareerist.ru/marketplace?utm_source=vk&amp;utm_medium=bio&amp;utm_campaign=profile</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1132,10 +1144,10 @@
         <v>37</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7" t="str">
@@ -1143,7 +1155,7 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1155,10 +1167,10 @@
         <v>37</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7" t="str">
@@ -1166,7 +1178,7 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=telegram&amp;utm_medium=story&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1178,10 +1190,10 @@
         <v>37</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7" t="str">
@@ -1189,7 +1201,7 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=telegram&amp;utm_medium=ads&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1201,10 +1213,10 @@
         <v>39</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7" t="str">
@@ -1212,7 +1224,7 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=vk&amp;utm_medium=post&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1224,10 +1236,10 @@
         <v>39</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7" t="str">
@@ -1235,7 +1247,7 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=vk&amp;utm_medium=story&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1247,10 +1259,10 @@
         <v>39</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7" t="str">
@@ -1258,7 +1270,7 @@
         <v>https://legalcareerist.ru/events/dzhazovyy-vecher-dlya-yuristov-2?utm_source=vk&amp;utm_medium=ads&amp;utm_campaign=legal_night_jazz_2</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1270,10 +1282,10 @@
         <v>37</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7" t="str">
@@ -1281,7 +1293,7 @@
         <v>https://legalcareerist.ru/kadry/vacancies?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=oktober_vacancies</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1293,10 +1305,10 @@
         <v>39</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7" t="str">
@@ -1304,7 +1316,7 @@
         <v>https://legalcareerist.ru/kadry/vacancies?utm_source=vk&amp;utm_medium=post&amp;utm_campaign=oktober_vacancies</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1316,10 +1328,10 @@
         <v>37</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7" t="str">
@@ -1327,7 +1339,7 @@
         <v>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=vacancy_tim_junior</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1339,10 +1351,10 @@
         <v>39</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7" t="str">
@@ -1350,116 +1362,146 @@
         <v>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim?utm_source=vk&amp;utm_medium=post&amp;utm_campaign=vacancy_tim_junior</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7" t="str">
         <f>IF(OR(IF(B27&lt;&gt;"",B27,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A27,'Справочник'!$A$5:$A$30,0)),""))="",C27="",D27="",E27=""),"",IF(B27&lt;&gt;"",B27,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A27,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B27&lt;&gt;"",B27,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A27,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C27&amp;"&amp;utm_medium="&amp;D27&amp;"&amp;utm_campaign="&amp;E27&amp;IF(F27&lt;&gt;"","&amp;utm_content="&amp;F27,""))</f>
-        <v>https://legalcareerist.ru/materials/longlist-studencheskie-yuridicheskie-meropriyatiya?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+        <v>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim?utm_source=telegram&amp;utm_medium=story&amp;utm_campaign=vacancy_tim_junior</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="6" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7" t="str">
         <f>IF(OR(IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),""))="",C28="",D28="",E28=""),"",IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B28&lt;&gt;"",B28,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A28,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C28&amp;"&amp;utm_medium="&amp;D28&amp;"&amp;utm_campaign="&amp;E28&amp;IF(F28&lt;&gt;"","&amp;utm_content="&amp;F28,""))</f>
-        <v>https://legalcareerist.ru/materials/gaid-kariera-yurista-v-notariate?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+        <v>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim?utm_source=instagram&amp;utm_medium=story&amp;utm_campaign=vacancy_tim_junior</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="6" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7" t="str">
         <f>IF(OR(IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),""))="",C29="",D29="",E29=""),"",IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B29&lt;&gt;"",B29,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A29,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C29&amp;"&amp;utm_medium="&amp;D29&amp;"&amp;utm_campaign="&amp;E29&amp;IF(F29&lt;&gt;"","&amp;utm_content="&amp;F29,""))</f>
+        <v>https://legalcareerist.ru/vacancies/mladshiy-yurist-tim?utm_source=vk&amp;utm_medium=story&amp;utm_campaign=vacancy_tim_junior</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7" t="str">
+        <f>IF(OR(IF(B30&lt;&gt;"",B30,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A30,'Справочник'!$A$5:$A$30,0)),""))="",C30="",D30="",E30=""),"",IF(B30&lt;&gt;"",B30,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A30,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B30&lt;&gt;"",B30,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A30,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C30&amp;"&amp;utm_medium="&amp;D30&amp;"&amp;utm_campaign="&amp;E30&amp;IF(F30&lt;&gt;"","&amp;utm_content="&amp;F30,""))</f>
+        <v>https://legalcareerist.ru/materials/longlist-studencheskie-yuridicheskie-meropriyatiya?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="7" t="str">
+        <f>IF(OR(IF(B31&lt;&gt;"",B31,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A31,'Справочник'!$A$5:$A$30,0)),""))="",C31="",D31="",E31=""),"",IF(B31&lt;&gt;"",B31,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A31,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B31&lt;&gt;"",B31,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A31,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C31&amp;"&amp;utm_medium="&amp;D31&amp;"&amp;utm_campaign="&amp;E31&amp;IF(F31&lt;&gt;"","&amp;utm_content="&amp;F31,""))</f>
+        <v>https://legalcareerist.ru/materials/gaid-kariera-yurista-v-notariate?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="7" t="str">
+        <f>IF(OR(IF(B32&lt;&gt;"",B32,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A32,'Справочник'!$A$5:$A$30,0)),""))="",C32="",D32="",E32=""),"",IF(B32&lt;&gt;"",B32,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A32,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B32&lt;&gt;"",B32,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A32,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C32&amp;"&amp;utm_medium="&amp;D32&amp;"&amp;utm_campaign="&amp;E32&amp;IF(F32&lt;&gt;"","&amp;utm_content="&amp;F32,""))</f>
         <v>https://legalcareerist.ru/materials/gaid-stipendii-i-granty?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=materials_oktober</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7">
-        <f>IF(OR(IF(B30&lt;&gt;"",B30,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A30,'Справочник'!$A$5:$A$30,0)),""))="",C30="",D30="",E30=""),"",IF(B30&lt;&gt;"",B30,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A30,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B30&lt;&gt;"",B30,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A30,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C30&amp;"&amp;utm_medium="&amp;D30&amp;"&amp;utm_campaign="&amp;E30&amp;IF(F30&lt;&gt;"","&amp;utm_content="&amp;F30,""))</f>
-        <v/>
-      </c>
-      <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7">
-        <f>IF(OR(IF(B31&lt;&gt;"",B31,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A31,'Справочник'!$A$5:$A$30,0)),""))="",C31="",D31="",E31=""),"",IF(B31&lt;&gt;"",B31,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A31,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B31&lt;&gt;"",B31,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A31,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C31&amp;"&amp;utm_medium="&amp;D31&amp;"&amp;utm_campaign="&amp;E31&amp;IF(F31&lt;&gt;"","&amp;utm_content="&amp;F31,""))</f>
-        <v/>
-      </c>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7">
-        <f>IF(OR(IF(B32&lt;&gt;"",B32,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A32,'Справочник'!$A$5:$A$30,0)),""))="",C32="",D32="",E32=""),"",IF(B32&lt;&gt;"",B32,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A32,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B32&lt;&gt;"",B32,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A32,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C32&amp;"&amp;utm_medium="&amp;D32&amp;"&amp;utm_campaign="&amp;E32&amp;IF(F32&lt;&gt;"","&amp;utm_content="&amp;F32,""))</f>
-        <v/>
-      </c>
-      <c r="H32" s="8"/>
+      <c r="H32" s="8" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="6"/>
@@ -3789,10 +3831,10 @@
         <v>38</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3809,10 +3851,10 @@
         <v>40</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3829,10 +3871,10 @@
         <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3849,10 +3891,10 @@
         <v>44</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3869,10 +3911,10 @@
         <v>46</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3889,10 +3931,10 @@
         <v>48</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3909,10 +3951,10 @@
         <v>50</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3929,10 +3971,10 @@
         <v>52</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3949,10 +3991,10 @@
         <v>54</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3978,8 +4020,12 @@
       <c r="B15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="8"/>
+      <c r="D15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="G15" s="6"/>
       <c r="H15" s="8"/>
     </row>
@@ -4155,87 +4201,87 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="42" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="42" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="42" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="42" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/docs/utm-ssylki.xlsx
+++ b/docs/utm-ssylki.xlsx
@@ -357,7 +357,7 @@
     <t>Бот</t>
   </si>
   <si>
-    <t>Метки работают только для ссылок на сайт. Ссылка на бота (t.me/…) ведёт в Telegram, а не на сайт; для неё используется параметр start, например https://t.me/legalcareerist_bot?start=tg_post_oktober.</t>
+    <t>Метки работают только для ссылок на сайт. Ссылка на бота (t.me/…) ведёт в Telegram, а не на сайт; для неё используется параметр start, например https://t.me/LegalcareeristBot?start=tg_post_oktober.</t>
   </si>
   <si>
     <t>Где смотреть результат</t>

--- a/docs/utm-ssylki.xlsx
+++ b/docs/utm-ssylki.xlsx
@@ -357,7 +357,7 @@
     <t>Бот</t>
   </si>
   <si>
-    <t>Метки работают только для ссылок на сайт. Ссылка на бота (t.me/…) ведёт в Telegram, а не на сайт; для неё используется параметр start, например https://t.me/LegalcareeristBot?start=tg_post_oktober.</t>
+    <t>Метки работают только для ссылок на сайт. Ссылка на бота (t.me/…) ведёт в Telegram, а не на сайт; для неё используется параметр start, например https://t.me/legalcareerist_bot?start=tg_post_oktober.</t>
   </si>
   <si>
     <t>Где смотреть результат</t>

--- a/docs/utm-ssylki.xlsx
+++ b/docs/utm-ssylki.xlsx
@@ -1504,30 +1504,70 @@
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Маркетплейс</t>
+        </is>
+      </c>
       <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>telegram</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>yugrbbb_marketplace</t>
+        </is>
+      </c>
       <c r="F33" s="6"/>
-      <c r="G33" s="7">
+      <c r="G33" s="7" t="str">
         <f>IF(OR(IF(B33&lt;&gt;"",B33,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A33,'Справочник'!$A$5:$A$30,0)),""))="",C33="",D33="",E33=""),"",IF(B33&lt;&gt;"",B33,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A33,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B33&lt;&gt;"",B33,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A33,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C33&amp;"&amp;utm_medium="&amp;D33&amp;"&amp;utm_campaign="&amp;E33&amp;IF(F33&lt;&gt;"","&amp;utm_content="&amp;F33,""))</f>
-        <v/>
-      </c>
-      <c r="H33" s="8"/>
+        <v>https://legalcareerist.ru/marketplace?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=yugrbbb_marketplace</v>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Telegram-блогер @yugrbbb (t.me/yugrbbb): переходы на маркетплейс</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Сообщество (подписка)</t>
+        </is>
+      </c>
       <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>telegram</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>yugrbbb_community</t>
+        </is>
+      </c>
       <c r="F34" s="6"/>
-      <c r="G34" s="7">
+      <c r="G34" s="7" t="str">
         <f>IF(OR(IF(B34&lt;&gt;"",B34,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A34,'Справочник'!$A$5:$A$30,0)),""))="",C34="",D34="",E34=""),"",IF(B34&lt;&gt;"",B34,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A34,'Справочник'!$A$5:$A$30,0)),""))&amp;IF(ISNUMBER(FIND("?",IF(B34&lt;&gt;"",B34,IFERROR(INDEX('Справочник'!$B$5:$B$30,MATCH(A34,'Справочник'!$A$5:$A$30,0)),"")))),"&amp;","?")&amp;"utm_source="&amp;C34&amp;"&amp;utm_medium="&amp;D34&amp;"&amp;utm_campaign="&amp;E34&amp;IF(F34&lt;&gt;"","&amp;utm_content="&amp;F34,""))</f>
-        <v/>
-      </c>
-      <c r="H34" s="8"/>
+        <v>https://legalcareerist.ru/community?utm_source=telegram&amp;utm_medium=post&amp;utm_campaign=yugrbbb_community</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Telegram-блогер @yugrbbb (t.me/yugrbbb): переходы в сообщество</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="6"/>
